--- a/Super_Simulador_Almacen.xlsx
+++ b/Super_Simulador_Almacen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\SIMULADOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF128F2-D886-472A-9865-3DB6E8B1AF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE306C4-8365-4DB0-A14B-BEEA2832B38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="646" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="646" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Simulador Península" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="165">
   <si>
     <t>SIMULADOR UNIFICADO - PENÍNSULA Y BALEARES</t>
   </si>
@@ -532,6 +532,9 @@
   </si>
   <si>
     <t>07157</t>
+  </si>
+  <si>
+    <t>Máx de 1000kg</t>
   </si>
 </sst>
 </file>
@@ -541,7 +544,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ \€"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -570,6 +573,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -594,7 +603,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -617,11 +626,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -655,6 +679,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1090,15 +1120,15 @@
       </c>
       <c r="D13" s="6">
         <f>IF(OR(C13="Canarias", C13="Especial"), "Ver Simulador Canarias", IFERROR(INDEX(Tarifas_DHL!B$2:I$23, MATCH(C$5, Tarifas_DHL!A$2:A$23, 1) + IF(ISNUMBER(MATCH(C$5, Tarifas_DHL!A$2:A$23, 0)), 0, 1), MATCH("Zona "&amp;C13, Tarifas_DHL!B$1:I$1, 0)), 0))</f>
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="E13" s="6">
         <f>IF(ISNUMBER(D13), D13*0.1015, 0)</f>
-        <v>1.4311500000000001</v>
+        <v>1.4413</v>
       </c>
       <c r="F13" s="7">
         <f>IF(ISNUMBER(D13), D13+E13, "N/A")</f>
-        <v>15.53115</v>
+        <v>15.641299999999999</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
@@ -2867,13 +2897,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>128</v>
       </c>
@@ -2899,576 +2929,732 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
+    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15">
+        <v>3</v>
+      </c>
+      <c r="B2" s="15">
         <v>3.92</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="15">
         <v>3.92</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="15">
         <v>3.92</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="15">
         <v>3.92</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="15">
         <v>3.92</v>
       </c>
-      <c r="G2">
-        <v>3.92</v>
-      </c>
-      <c r="H2">
+      <c r="G2" s="15">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="H2" s="15">
         <v>6.42</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="15">
         <v>4</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="15">
         <v>4.13</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="15">
         <v>4.18</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="15">
         <v>4.18</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="15">
         <v>4.13</v>
       </c>
-      <c r="G3">
-        <v>4.24</v>
-      </c>
-      <c r="H3">
-        <v>6.42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="G3" s="15">
+        <v>9.24</v>
+      </c>
+      <c r="H3" s="15">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="15">
         <v>10</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="15">
         <v>4.37</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="15">
+        <v>4.51</v>
+      </c>
+      <c r="D4" s="15">
         <v>4.91</v>
       </c>
-      <c r="D4">
+      <c r="E4" s="15">
         <v>4.91</v>
       </c>
-      <c r="E4">
-        <v>4.41</v>
-      </c>
-      <c r="F4">
-        <v>4.12</v>
-      </c>
-      <c r="G4">
-        <v>4.87</v>
-      </c>
-      <c r="H4">
-        <v>6.42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="F4" s="15">
+        <v>4.91</v>
+      </c>
+      <c r="G4" s="15">
+        <v>10.1</v>
+      </c>
+      <c r="H4" s="15">
+        <v>9.8699999999999992</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15">
         <v>20</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="15">
         <v>4.37</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="15">
+        <v>6.5</v>
+      </c>
+      <c r="D5" s="15">
         <v>6.9</v>
       </c>
-      <c r="D5">
+      <c r="E5" s="15">
         <v>6.9</v>
       </c>
-      <c r="E5">
+      <c r="F5" s="15">
         <v>6.9</v>
       </c>
-      <c r="F5">
-        <v>5.5</v>
-      </c>
-      <c r="G5">
-        <v>8.7799999999999994</v>
-      </c>
-      <c r="H5">
-        <v>14.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="G5" s="15">
+        <v>11.78</v>
+      </c>
+      <c r="H5" s="15">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15">
         <v>30</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="15">
         <v>5.14</v>
       </c>
-      <c r="C6">
-        <v>7.14</v>
-      </c>
-      <c r="D6">
+      <c r="C6" s="15">
+        <v>7.34</v>
+      </c>
+      <c r="D6" s="15">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="E6" s="15">
         <v>9.15</v>
       </c>
-      <c r="E6">
-        <v>9.25</v>
-      </c>
-      <c r="F6">
-        <v>11.3</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="15">
+        <v>9.15</v>
+      </c>
+      <c r="G6" s="15">
+        <v>13.38</v>
+      </c>
+      <c r="H6" s="15">
         <v>18.41</v>
       </c>
-      <c r="H6">
-        <v>18.41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7">
+    </row>
+    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="15">
         <v>40</v>
       </c>
-      <c r="B7">
-        <v>5.14</v>
-      </c>
-      <c r="C7">
-        <v>7.14</v>
-      </c>
-      <c r="D7">
+      <c r="B7" s="15">
+        <v>6.07</v>
+      </c>
+      <c r="C7" s="15">
+        <v>8.65</v>
+      </c>
+      <c r="D7" s="15">
+        <v>9.76</v>
+      </c>
+      <c r="E7" s="15">
         <v>11.13</v>
       </c>
-      <c r="E7">
-        <v>11.18</v>
-      </c>
-      <c r="F7">
-        <v>13.84</v>
-      </c>
-      <c r="G7">
-        <v>22.3</v>
-      </c>
-      <c r="H7">
-        <v>22.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="F7" s="15">
+        <v>11.13</v>
+      </c>
+      <c r="G7" s="15">
+        <v>15.84</v>
+      </c>
+      <c r="H7" s="15">
+        <v>22.38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15">
         <v>50</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="15">
         <v>6.9</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="15">
+        <v>9.91</v>
+      </c>
+      <c r="D8" s="15">
         <v>11.17</v>
       </c>
-      <c r="D8">
+      <c r="E8" s="15">
         <v>12.72</v>
       </c>
-      <c r="E8">
+      <c r="F8" s="15">
         <v>12.72</v>
       </c>
-      <c r="F8">
-        <v>15.83</v>
-      </c>
-      <c r="G8">
+      <c r="G8" s="15">
+        <v>15.82</v>
+      </c>
+      <c r="H8" s="15">
         <v>25.61</v>
       </c>
-      <c r="H8">
-        <v>25.61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9">
+    </row>
+    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15">
         <v>60</v>
       </c>
-      <c r="B9">
-        <v>7.78</v>
-      </c>
-      <c r="C9">
+      <c r="B9" s="15">
+        <v>7.75</v>
+      </c>
+      <c r="C9" s="15">
         <v>11.19</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="15">
         <v>12.6</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="15">
         <v>14.34</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="15">
         <v>14.34</v>
       </c>
-      <c r="G9">
-        <v>28.6</v>
-      </c>
-      <c r="H9">
-        <v>28.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="G9" s="15">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="H9" s="15">
+        <v>28.86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15">
         <v>70</v>
       </c>
-      <c r="B10">
-        <v>7.78</v>
-      </c>
-      <c r="C10">
+      <c r="B10" s="15">
+        <v>8.6</v>
+      </c>
+      <c r="C10" s="15">
         <v>12.46</v>
       </c>
-      <c r="D10">
-        <v>14.07</v>
-      </c>
-      <c r="E10">
+      <c r="D10" s="15">
+        <v>14.02</v>
+      </c>
+      <c r="E10" s="15">
         <v>15.97</v>
       </c>
-      <c r="F10">
-        <v>15.87</v>
-      </c>
-      <c r="G10">
+      <c r="F10" s="15">
+        <v>15.97</v>
+      </c>
+      <c r="G10" s="15">
+        <v>19.86</v>
+      </c>
+      <c r="H10" s="15">
         <v>32.119999999999997</v>
       </c>
-      <c r="H10">
-        <v>32.119999999999997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11">
+    </row>
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15">
         <v>80</v>
       </c>
-      <c r="B11">
-        <v>11.71</v>
-      </c>
-      <c r="C11">
+      <c r="B11" s="15">
+        <v>12.54</v>
+      </c>
+      <c r="C11" s="15">
         <v>18.190000000000001</v>
       </c>
-      <c r="D11">
-        <v>20.41</v>
-      </c>
-      <c r="E11">
+      <c r="D11" s="15">
+        <v>20.46</v>
+      </c>
+      <c r="E11" s="15">
         <v>20.71</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="15">
         <v>20.71</v>
       </c>
-      <c r="G11">
-        <v>45.37</v>
-      </c>
-      <c r="H11">
-        <v>45.37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="G11" s="15">
+        <v>28.97</v>
+      </c>
+      <c r="H11" s="15">
+        <v>46.87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15">
         <v>90</v>
       </c>
-      <c r="B12">
-        <v>11.71</v>
-      </c>
-      <c r="C12">
+      <c r="B12" s="15">
+        <v>13.71</v>
+      </c>
+      <c r="C12" s="15">
         <v>19.79</v>
       </c>
-      <c r="D12">
-        <v>22.36</v>
-      </c>
-      <c r="E12">
+      <c r="D12" s="15">
         <v>22.26</v>
       </c>
-      <c r="F12">
+      <c r="E12" s="15">
         <v>22.26</v>
       </c>
-      <c r="G12">
+      <c r="F12" s="15">
+        <v>22.26</v>
+      </c>
+      <c r="G12" s="15">
+        <v>31.53</v>
+      </c>
+      <c r="H12" s="15">
         <v>50.98</v>
       </c>
-      <c r="H12">
-        <v>50.98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13">
+    </row>
+    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15">
         <v>100</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="15">
         <v>14.9</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="15">
         <v>21.53</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="15">
         <v>22.48</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="15">
         <v>22.48</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="15">
         <v>22.48</v>
       </c>
-      <c r="G13">
-        <v>50.98</v>
-      </c>
-      <c r="H13">
-        <v>54.32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="G13" s="15">
+        <v>34.32</v>
+      </c>
+      <c r="H13" s="15">
+        <v>55.51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="15">
         <v>125</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="15">
         <v>16.77</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="15">
         <v>24.49</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="15">
         <v>25.56</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="15">
         <v>25.56</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="15">
         <v>25.56</v>
       </c>
-      <c r="G14">
-        <v>53.15</v>
-      </c>
-      <c r="H14">
+      <c r="G14" s="15">
+        <v>39.020000000000003</v>
+      </c>
+      <c r="H14" s="15">
         <v>63.15</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15">
+    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="15">
         <v>150</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="15">
         <v>19.66</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="15">
+        <v>27.57</v>
+      </c>
+      <c r="D15" s="15">
         <v>29.78</v>
       </c>
-      <c r="D15">
+      <c r="E15" s="15">
         <v>29.78</v>
       </c>
-      <c r="E15">
+      <c r="F15" s="15">
         <v>29.78</v>
       </c>
-      <c r="F15">
-        <v>26.78</v>
-      </c>
-      <c r="G15">
-        <v>65.45</v>
-      </c>
-      <c r="H15">
+      <c r="G15" s="15">
+        <v>45.45</v>
+      </c>
+      <c r="H15" s="15">
         <v>73.52</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16">
+    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="15">
         <v>175</v>
       </c>
-      <c r="B16">
-        <v>21.99</v>
-      </c>
-      <c r="C16">
-        <v>29.78</v>
-      </c>
-      <c r="D16">
-        <v>31.57</v>
-      </c>
-      <c r="E16">
-        <v>31.57</v>
-      </c>
-      <c r="F16">
+      <c r="B16" s="15">
+        <v>22.99</v>
+      </c>
+      <c r="C16" s="15">
+        <v>33.35</v>
+      </c>
+      <c r="D16" s="15">
         <v>33.57</v>
       </c>
-      <c r="G16">
-        <v>72.36</v>
-      </c>
-      <c r="H16">
+      <c r="E16" s="15">
+        <v>33.57</v>
+      </c>
+      <c r="F16" s="15">
+        <v>33.57</v>
+      </c>
+      <c r="G16" s="15">
+        <v>53.16</v>
+      </c>
+      <c r="H16" s="15">
         <v>85.97</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17">
+    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="15">
         <v>200</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="15">
         <v>25.78</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="15">
         <v>37.82</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="15">
         <v>37.56</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="15">
         <v>37.56</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="15">
         <v>37.56</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="15">
+        <v>59.47</v>
+      </c>
+      <c r="H17" s="15">
         <v>96.2</v>
       </c>
-      <c r="H17">
-        <v>96.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18">
+    </row>
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="15">
         <v>250</v>
       </c>
-      <c r="B18">
-        <v>29.77</v>
-      </c>
-      <c r="C18">
+      <c r="B18" s="15">
+        <v>29.27</v>
+      </c>
+      <c r="C18" s="15">
         <v>42.51</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="15">
         <v>42.79</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="15">
         <v>42.79</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="15">
         <v>42.79</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="15">
+        <v>67.739999999999995</v>
+      </c>
+      <c r="H18" s="15">
         <v>109.52</v>
       </c>
-      <c r="H18">
-        <v>109.52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19">
+    </row>
+    <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="15">
         <v>300</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="15">
         <v>32.83</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="15">
         <v>48.03</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="15">
         <v>48.34</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="15">
         <v>48.34</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="15">
         <v>48.34</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="15">
+        <v>76.52</v>
+      </c>
+      <c r="H19" s="15">
         <v>123.75</v>
       </c>
-      <c r="H19">
-        <v>123.75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20">
+    </row>
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="15">
         <v>350</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="15">
         <v>44.47</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="15">
         <v>65.38</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="15">
         <v>67.069999999999993</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="15">
         <v>73.540000000000006</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="15">
         <v>81.16</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="15">
+        <v>104.25</v>
+      </c>
+      <c r="H20" s="15">
         <v>168.54</v>
       </c>
-      <c r="H20">
-        <v>168.54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21">
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="15">
         <v>400</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="15">
         <v>49.01</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="15">
         <v>72.28</v>
       </c>
-      <c r="D21">
-        <v>74.11</v>
-      </c>
-      <c r="E21">
-        <v>74.11</v>
-      </c>
-      <c r="F21">
+      <c r="D21" s="15">
+        <v>74.13</v>
+      </c>
+      <c r="E21" s="15">
+        <v>81.69</v>
+      </c>
+      <c r="F21" s="15">
         <v>89.68</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="15">
+        <v>115.19</v>
+      </c>
+      <c r="H21" s="15">
         <v>186.27</v>
       </c>
-      <c r="H21">
-        <v>186.27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22">
+    </row>
+    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="15">
         <v>450</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="15">
         <v>53.02</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="15">
         <v>79.209999999999994</v>
       </c>
-      <c r="D22">
-        <v>80.13</v>
-      </c>
-      <c r="E22">
+      <c r="D22" s="15">
+        <v>89.13</v>
+      </c>
+      <c r="E22" s="15">
         <v>89.56</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="15">
         <v>89.56</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="15">
+        <v>126.26</v>
+      </c>
+      <c r="H22" s="15">
         <v>204.19</v>
       </c>
-      <c r="H22">
-        <v>204.19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23">
+    </row>
+    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="15">
         <v>500</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="15">
         <v>57.34</v>
       </c>
-      <c r="C23">
-        <v>86.1</v>
-      </c>
-      <c r="D23">
+      <c r="C23" s="15">
+        <v>86.49</v>
+      </c>
+      <c r="D23" s="15">
         <v>97.28</v>
       </c>
-      <c r="E23">
-        <v>97.27</v>
-      </c>
-      <c r="F23">
-        <v>97.27</v>
-      </c>
-      <c r="G23">
+      <c r="E23" s="15">
+        <v>97.77</v>
+      </c>
+      <c r="F23" s="15">
+        <v>97.77</v>
+      </c>
+      <c r="G23" s="15">
+        <v>137.84</v>
+      </c>
+      <c r="H23" s="15">
         <v>222.9</v>
       </c>
-      <c r="H23">
-        <v>222.9</v>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="15">
+        <v>600</v>
+      </c>
+      <c r="B24" s="15">
+        <v>66.91</v>
+      </c>
+      <c r="C24" s="15">
+        <v>106.7</v>
+      </c>
+      <c r="D24" s="15">
+        <v>120.08</v>
+      </c>
+      <c r="E24" s="15">
+        <v>124.6</v>
+      </c>
+      <c r="F24" s="15">
+        <v>130.05000000000001</v>
+      </c>
+      <c r="G24" s="15">
+        <v>170.08</v>
+      </c>
+      <c r="H24" s="15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="15">
+        <v>700</v>
+      </c>
+      <c r="B25" s="15">
+        <v>75.19</v>
+      </c>
+      <c r="C25" s="15">
+        <v>121.4</v>
+      </c>
+      <c r="D25" s="15">
+        <v>136.58000000000001</v>
+      </c>
+      <c r="E25" s="15">
+        <v>155.55000000000001</v>
+      </c>
+      <c r="F25" s="15">
+        <v>170.73</v>
+      </c>
+      <c r="G25" s="15">
+        <v>199.48</v>
+      </c>
+      <c r="H25" s="15">
+        <v>312.88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="15">
+        <v>800</v>
+      </c>
+      <c r="B26" s="15">
+        <v>82.9</v>
+      </c>
+      <c r="C26" s="15">
+        <v>136.26</v>
+      </c>
+      <c r="D26" s="15">
+        <v>153.28</v>
+      </c>
+      <c r="E26" s="15">
+        <v>174.9</v>
+      </c>
+      <c r="F26" s="15">
+        <v>191.04</v>
+      </c>
+      <c r="G26" s="15">
+        <v>217.21</v>
+      </c>
+      <c r="H26" s="15">
+        <v>351.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="15">
+        <v>900</v>
+      </c>
+      <c r="B27" s="15">
+        <v>91.39</v>
+      </c>
+      <c r="C27" s="15">
+        <v>151.38</v>
+      </c>
+      <c r="D27" s="15">
+        <v>170.27</v>
+      </c>
+      <c r="E27" s="15">
+        <v>193.95</v>
+      </c>
+      <c r="F27" s="15">
+        <v>212.87</v>
+      </c>
+      <c r="G27" s="15">
+        <v>241.24</v>
+      </c>
+      <c r="H27" s="15">
+        <v>390.14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="15">
+        <v>1000</v>
+      </c>
+      <c r="B28" s="15">
+        <v>100.79</v>
+      </c>
+      <c r="C28" s="15">
+        <v>168.58</v>
+      </c>
+      <c r="D28" s="15">
+        <v>189.64</v>
+      </c>
+      <c r="E28" s="15">
+        <v>215.98</v>
+      </c>
+      <c r="F28" s="15">
+        <v>237.06</v>
+      </c>
+      <c r="G28" s="15">
+        <v>268.67</v>
+      </c>
+      <c r="H28" s="15">
+        <v>434.49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B29" s="15">
+        <v>9.18</v>
+      </c>
+      <c r="C29" s="15">
+        <v>33.32</v>
+      </c>
+      <c r="D29" s="15">
+        <v>34.11</v>
+      </c>
+      <c r="E29" s="15">
+        <v>34.9</v>
+      </c>
+      <c r="F29" s="15">
+        <v>35.020000000000003</v>
+      </c>
+      <c r="G29" s="15">
+        <v>38.549999999999997</v>
+      </c>
+      <c r="H29" s="15">
+        <v>61.86</v>
       </c>
     </row>
   </sheetData>
